--- a/resources/library/xlsx/swot-analysis.xlsx
+++ b/resources/library/xlsx/swot-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWOT" sheetId="1" r:id="R58ede0442b7944bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" r:id="Rbf68a8b2794e4ccf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R4ea8cf8a0fea4641"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWOT" sheetId="1" r:id="R7cf09cc20f154059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" r:id="R599b608ac2724217"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="R511b1e063fe44243"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -158,6 +158,102 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="07340169-a829-466c-bd48-85a1e2a32b37"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8bc755ce596b429b"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="b69ea665-81c4-4e9c-841e-bb48fa0a8a7c"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf24606061d374116"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1657350" cy="552450"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="acf58440-f9af-4ad0-916f-a97966e19c8d"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R15e91ae244f74a0f"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -361,7 +457,7 @@
     <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -1448,6 +1544,7 @@
     <x:mergeCell ref="A2:H2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bd8e6e86e4f40f1"/>
 </x:worksheet>
 </file>
 
@@ -1464,7 +1561,7 @@
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -2573,6 +2670,7 @@
     <x:mergeCell ref="A2:G2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b94849e84074307"/>
 </x:worksheet>
 </file>
 
@@ -2587,7 +2685,7 @@
     <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
+    <x:row r="1" ht="48" hidden="0" customHeight="1">
       <x:c r="A1" s="12"/>
       <x:c r="B1" s="12"/>
       <x:c r="C1" s="12"/>
@@ -3649,5 +3747,6 @@
     <x:mergeCell ref="A5:H5"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93de1f1657804f7a"/>
 </x:worksheet>
 </file>